--- a/artfynd/A 56516-2025 artfynd.xlsx
+++ b/artfynd/A 56516-2025 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121343359</v>
+        <v>121343358</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437850</v>
+        <v>437654</v>
       </c>
       <c r="R2" t="n">
-        <v>6857645</v>
+        <v>6857760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121343362</v>
+        <v>121343359</v>
       </c>
       <c r="B3" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437910</v>
+        <v>437850</v>
       </c>
       <c r="R3" t="n">
-        <v>6857518</v>
+        <v>6857645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121343363</v>
+        <v>121343361</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437909</v>
+        <v>437886</v>
       </c>
       <c r="R4" t="n">
-        <v>6857517</v>
+        <v>6857532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343358</v>
+        <v>121343362</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437654</v>
+        <v>437910</v>
       </c>
       <c r="R5" t="n">
-        <v>6857760</v>
+        <v>6857518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343361</v>
+        <v>121343363</v>
       </c>
       <c r="B6" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437886</v>
+        <v>437909</v>
       </c>
       <c r="R6" t="n">
-        <v>6857532</v>
+        <v>6857517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,12 +1188,7 @@
         <v>121343357</v>
       </c>
       <c r="B7" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56516-2025 artfynd.xlsx
+++ b/artfynd/A 56516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343358</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343361</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343362</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343363</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>